--- a/13156_Cuenca_Caplina/_raw_reportes_xlsx/IDConfig_7742_completo.xlsx
+++ b/13156_Cuenca_Caplina/_raw_reportes_xlsx/IDConfig_7742_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R2255998ee4bc48de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R036a56dda80343d8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,1386 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.5250</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4590</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3850</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3650</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.5200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4670</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.5340</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.5590</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4460</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4870</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4990</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.5180</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4610</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4410</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4370</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4970</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4650</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7530</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4870</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4970</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.5310</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.6210</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.5340</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4930</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.5220</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.5690</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.5720</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.5240</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.5460</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.5110</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.5590</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.5180</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.5050</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.5310</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4830</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4590</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.5100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4910</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.5500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4960</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4850</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.5020</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4510</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4760</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.5400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4860</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4870</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4840</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    439.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.5500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4470</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4950</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.5040</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.5060</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.5230</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4940</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4410</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3690</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3340</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3350</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3990</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4320</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3420</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3150</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3550</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4250</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4110</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4690</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3740</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3220</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3010</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2690</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3660</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4090</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3710</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3240</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3550</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3280</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2730</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>30/06/2026</x:t>
         </x:is>
       </x:c>
@@ -760,6 +2140,21 @@
       </x:c>
       <x:c s="3">
         <x:v>      0.5600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.5710</x:v>
       </x:c>
     </x:row>
     <x:row>
